--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G657"/>
+  <dimension ref="A1:G658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18175,6 +18175,33 @@
         <v>346.94</v>
       </c>
       <c r="G657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="C658" t="n">
+        <v>374.84</v>
+      </c>
+      <c r="D658" t="n">
+        <v>363.89</v>
+      </c>
+      <c r="E658" t="n">
+        <v>357.57</v>
+      </c>
+      <c r="F658" t="n">
+        <v>349.86</v>
+      </c>
+      <c r="G658" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18191,7 +18218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B717"/>
+  <dimension ref="A1:B718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25363,6 +25390,16 @@
         </is>
       </c>
       <c r="B717" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
         <v>-0.43</v>
       </c>
     </row>
@@ -25532,28 +25569,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6110062023705407</v>
+        <v>-0.6055227132541963</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K2" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1602670218206984</v>
+        <v>0.1577262189042924</v>
       </c>
       <c r="M2" t="n">
-        <v>8.303469400373878</v>
+        <v>8.316700849906308</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1239425603415</v>
+        <v>108.4392942470544</v>
       </c>
       <c r="O2" t="n">
-        <v>10.39826632474575</v>
+        <v>10.41341895090438</v>
       </c>
       <c r="P2" t="n">
-        <v>372.4993076423294</v>
+        <v>372.4434993171753</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25610,28 +25647,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5907574582562922</v>
+        <v>-0.5853142312420664</v>
       </c>
       <c r="J3" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K3" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1529357058375441</v>
+        <v>0.1504301348428899</v>
       </c>
       <c r="M3" t="n">
-        <v>8.461579682863389</v>
+        <v>8.474695270864304</v>
       </c>
       <c r="N3" t="n">
-        <v>106.8463038686153</v>
+        <v>107.1565784746469</v>
       </c>
       <c r="O3" t="n">
-        <v>10.33664858010638</v>
+        <v>10.35164617221082</v>
       </c>
       <c r="P3" t="n">
-        <v>372.7214656252664</v>
+        <v>372.6660670684987</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25688,28 +25725,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6234396573942934</v>
+        <v>-0.6198486075297682</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K4" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1683117865701727</v>
+        <v>0.1669125089486159</v>
       </c>
       <c r="M4" t="n">
-        <v>8.220577087196903</v>
+        <v>8.226397688643818</v>
       </c>
       <c r="N4" t="n">
-        <v>106.1618453360495</v>
+        <v>106.2060860681625</v>
       </c>
       <c r="O4" t="n">
-        <v>10.30348704740533</v>
+        <v>10.30563370531684</v>
       </c>
       <c r="P4" t="n">
-        <v>368.6428855619794</v>
+        <v>368.6063375768859</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25766,28 +25803,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4866565830015327</v>
+        <v>-0.4843828985987578</v>
       </c>
       <c r="J5" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K5" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09946742009978382</v>
+        <v>0.09887787551752836</v>
       </c>
       <c r="M5" t="n">
-        <v>8.673766786617939</v>
+        <v>8.672046060588366</v>
       </c>
       <c r="N5" t="n">
-        <v>118.5215639773619</v>
+        <v>118.4236781731968</v>
       </c>
       <c r="O5" t="n">
-        <v>10.88676094976655</v>
+        <v>10.88226438629373</v>
       </c>
       <c r="P5" t="n">
-        <v>362.998398201487</v>
+        <v>362.9752577309297</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25844,28 +25881,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.384291555819815</v>
+        <v>-0.383556294598434</v>
       </c>
       <c r="J6" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K6" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06677021654599913</v>
+        <v>0.06674267473951379</v>
       </c>
       <c r="M6" t="n">
-        <v>8.291882469482328</v>
+        <v>8.282913576488182</v>
       </c>
       <c r="N6" t="n">
-        <v>114.0935470557264</v>
+        <v>113.9285173164462</v>
       </c>
       <c r="O6" t="n">
-        <v>10.68145809595892</v>
+        <v>10.67373024375481</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5940342486767</v>
+        <v>357.5865511122201</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25903,7 +25940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G657"/>
+  <dimension ref="A1:G658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50215,6 +50252,43 @@
         </is>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-40.92663437249484,176.18649523135642</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-40.92702972786302,176.185765222687</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-40.92734138352988,176.18495332493012</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-40.92768650083476,176.18417416885714</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-40.928021568729974,176.18338518347025</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G658"/>
+  <dimension ref="A1:G659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18202,6 +18202,33 @@
         <v>349.86</v>
       </c>
       <c r="G658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:55:07+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>378.85</v>
+      </c>
+      <c r="C659" t="n">
+        <v>378.95</v>
+      </c>
+      <c r="D659" t="n">
+        <v>366.25</v>
+      </c>
+      <c r="E659" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="F659" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="G659" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18218,7 +18245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B718"/>
+  <dimension ref="A1:B719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25401,6 +25428,16 @@
       </c>
       <c r="B718" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-02-04 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -25569,28 +25606,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6055227132541963</v>
+        <v>-0.5985688725114876</v>
       </c>
       <c r="J2" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K2" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1577262189042924</v>
+        <v>0.1542274808618889</v>
       </c>
       <c r="M2" t="n">
-        <v>8.316700849906308</v>
+        <v>8.336674625837171</v>
       </c>
       <c r="N2" t="n">
-        <v>108.4392942470544</v>
+        <v>109.0349571553655</v>
       </c>
       <c r="O2" t="n">
-        <v>10.41341895090438</v>
+        <v>10.44198051881756</v>
       </c>
       <c r="P2" t="n">
-        <v>372.4434993171753</v>
+        <v>372.3723282625285</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25647,28 +25684,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5853142312420664</v>
+        <v>-0.5785635738068245</v>
       </c>
       <c r="J3" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K3" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1504301348428899</v>
+        <v>0.1470929720321006</v>
       </c>
       <c r="M3" t="n">
-        <v>8.474695270864304</v>
+        <v>8.493997834519202</v>
       </c>
       <c r="N3" t="n">
-        <v>107.1565784746469</v>
+        <v>107.7104002394456</v>
       </c>
       <c r="O3" t="n">
-        <v>10.35164617221082</v>
+        <v>10.37836211737891</v>
       </c>
       <c r="P3" t="n">
-        <v>372.6660670684987</v>
+        <v>372.5969755510191</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25725,28 +25762,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6198486075297682</v>
+        <v>-0.6154947448761955</v>
       </c>
       <c r="J4" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K4" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1669125089486159</v>
+        <v>0.1650599269504804</v>
       </c>
       <c r="M4" t="n">
-        <v>8.226397688643818</v>
+        <v>8.235872767916566</v>
       </c>
       <c r="N4" t="n">
-        <v>106.2060860681625</v>
+        <v>106.3427901778686</v>
       </c>
       <c r="O4" t="n">
-        <v>10.30563370531684</v>
+        <v>10.3122640665311</v>
       </c>
       <c r="P4" t="n">
-        <v>368.6063375768859</v>
+        <v>368.5617767351429</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25803,28 +25840,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4843828985987578</v>
+        <v>-0.4813447629648548</v>
       </c>
       <c r="J5" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K5" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09887787551752836</v>
+        <v>0.09796495894500135</v>
       </c>
       <c r="M5" t="n">
-        <v>8.672046060588366</v>
+        <v>8.674014653982223</v>
       </c>
       <c r="N5" t="n">
-        <v>118.4236781731968</v>
+        <v>118.3888618718359</v>
       </c>
       <c r="O5" t="n">
-        <v>10.88226438629373</v>
+        <v>10.88066458778304</v>
       </c>
       <c r="P5" t="n">
-        <v>362.9752577309297</v>
+        <v>362.9441630704069</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25881,28 +25918,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.383556294598434</v>
+        <v>-0.3817622170405786</v>
       </c>
       <c r="J6" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K6" t="n">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06674267473951379</v>
+        <v>0.06635137328577445</v>
       </c>
       <c r="M6" t="n">
-        <v>8.282913576488182</v>
+        <v>8.279124260629652</v>
       </c>
       <c r="N6" t="n">
-        <v>113.9285173164462</v>
+        <v>113.8059924630608</v>
       </c>
       <c r="O6" t="n">
-        <v>10.67373024375481</v>
+        <v>10.66798914805695</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5865511122201</v>
+        <v>357.568189116794</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25940,7 +25977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G658"/>
+  <dimension ref="A1:G659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50289,6 +50326,43 @@
         </is>
       </c>
     </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:55:07+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-40.92666790898229,176.18652804367116</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-40.92705943380205,176.18579428701904</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-40.92735844104253,176.18497001387925</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-40.92770377526253,176.1841910699148</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-40.92804585423528,176.18340894389308</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G659"/>
+  <dimension ref="A1:G660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18229,6 +18229,33 @@
         <v>353.22</v>
       </c>
       <c r="G659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>378.94</v>
+      </c>
+      <c r="C660" t="n">
+        <v>380.11</v>
+      </c>
+      <c r="D660" t="n">
+        <v>367.09</v>
+      </c>
+      <c r="E660" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="F660" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="G660" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18245,7 +18272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B719"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25438,6 +25465,16 @@
       </c>
       <c r="B719" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -25606,28 +25643,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5985688725114876</v>
+        <v>-0.591605831542412</v>
       </c>
       <c r="J2" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K2" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1542274808618889</v>
+        <v>0.1507607169935014</v>
       </c>
       <c r="M2" t="n">
-        <v>8.336674625837171</v>
+        <v>8.356947168416152</v>
       </c>
       <c r="N2" t="n">
-        <v>109.0349571553655</v>
+        <v>109.6300682482157</v>
       </c>
       <c r="O2" t="n">
-        <v>10.44198051881756</v>
+        <v>10.47043782504894</v>
       </c>
       <c r="P2" t="n">
-        <v>372.3723282625285</v>
+        <v>372.3008743003147</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25684,28 +25721,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5785635738068245</v>
+        <v>-0.5714732637761807</v>
       </c>
       <c r="J3" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K3" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1470929720321006</v>
+        <v>0.1435620191121457</v>
       </c>
       <c r="M3" t="n">
-        <v>8.493997834519202</v>
+        <v>8.515263279526907</v>
       </c>
       <c r="N3" t="n">
-        <v>107.7104002394456</v>
+        <v>108.3355783246873</v>
       </c>
       <c r="O3" t="n">
-        <v>10.37836211737891</v>
+        <v>10.40843784266819</v>
       </c>
       <c r="P3" t="n">
-        <v>372.5969755510191</v>
+        <v>372.5242155676635</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25762,28 +25799,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6154947448761955</v>
+        <v>-0.6108859869374814</v>
       </c>
       <c r="J4" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K4" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1650599269504804</v>
+        <v>0.1630539964146344</v>
       </c>
       <c r="M4" t="n">
-        <v>8.235872767916566</v>
+        <v>8.246486251106178</v>
       </c>
       <c r="N4" t="n">
-        <v>106.3427901778686</v>
+        <v>106.5146217427493</v>
       </c>
       <c r="O4" t="n">
-        <v>10.3122640665311</v>
+        <v>10.32059212171226</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5617767351429</v>
+        <v>368.5144821669983</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25840,28 +25877,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4813447629648548</v>
+        <v>-0.4783250464284309</v>
       </c>
       <c r="J5" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K5" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09796495894500135</v>
+        <v>0.09706226342279678</v>
       </c>
       <c r="M5" t="n">
-        <v>8.674014653982223</v>
+        <v>8.675873993712356</v>
       </c>
       <c r="N5" t="n">
-        <v>118.3888618718359</v>
+        <v>118.3522572267435</v>
       </c>
       <c r="O5" t="n">
-        <v>10.88066458778304</v>
+        <v>10.87898236172591</v>
       </c>
       <c r="P5" t="n">
-        <v>362.9441630704069</v>
+        <v>362.9131750707314</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25918,28 +25955,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3817622170405786</v>
+        <v>-0.3798048046986688</v>
       </c>
       <c r="J6" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K6" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06635137328577445</v>
+        <v>0.06590234123425343</v>
       </c>
       <c r="M6" t="n">
-        <v>8.279124260629652</v>
+        <v>8.276142998897209</v>
       </c>
       <c r="N6" t="n">
-        <v>113.8059924630608</v>
+        <v>113.6934015409076</v>
       </c>
       <c r="O6" t="n">
-        <v>10.66798914805695</v>
+        <v>10.66271079702097</v>
       </c>
       <c r="P6" t="n">
-        <v>357.568189116794</v>
+        <v>357.5481023661721</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25977,7 +26014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G659"/>
+  <dimension ref="A1:G660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50363,6 +50400,43 @@
         </is>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-40.92666855947441,176.18652868011725</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-40.92706781795849,176.18580249009563</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-40.92736451235992,176.18497595401575</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-40.927703413872855,176.18419071633608</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-40.92804968498409,176.18341269181855</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G660"/>
+  <dimension ref="A1:G662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18256,6 +18256,60 @@
         <v>353.75</v>
       </c>
       <c r="G660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="C661" t="n">
+        <v>379</v>
+      </c>
+      <c r="D661" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="E661" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="F661" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="C662" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="D662" t="n">
+        <v>365</v>
+      </c>
+      <c r="E662" t="n">
+        <v>357.79</v>
+      </c>
+      <c r="F662" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="G662" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18272,7 +18326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25475,6 +25529,26 @@
       </c>
       <c r="B720" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -25643,28 +25717,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.591605831542412</v>
+        <v>-0.5787609949274131</v>
       </c>
       <c r="J2" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K2" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1507607169935014</v>
+        <v>0.1446272573712166</v>
       </c>
       <c r="M2" t="n">
-        <v>8.356947168416152</v>
+        <v>8.392670436141518</v>
       </c>
       <c r="N2" t="n">
-        <v>109.6300682482157</v>
+        <v>110.6041997142895</v>
       </c>
       <c r="O2" t="n">
-        <v>10.47043782504894</v>
+        <v>10.51685312792232</v>
       </c>
       <c r="P2" t="n">
-        <v>372.3008743003147</v>
+        <v>372.1688840371821</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25721,28 +25795,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5714732637761807</v>
+        <v>-0.5586881912676819</v>
       </c>
       <c r="J3" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K3" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1435620191121457</v>
+        <v>0.1375112113987949</v>
       </c>
       <c r="M3" t="n">
-        <v>8.515263279526907</v>
+        <v>8.551741006181931</v>
       </c>
       <c r="N3" t="n">
-        <v>108.3355783246873</v>
+        <v>109.300509579896</v>
       </c>
       <c r="O3" t="n">
-        <v>10.40843784266819</v>
+        <v>10.45468840185569</v>
       </c>
       <c r="P3" t="n">
-        <v>372.5242155676635</v>
+        <v>372.3928389424274</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25799,28 +25873,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6108859869374814</v>
+        <v>-0.6027692558256675</v>
       </c>
       <c r="J4" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K4" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1630539964146344</v>
+        <v>0.1597253242980291</v>
       </c>
       <c r="M4" t="n">
-        <v>8.246486251106178</v>
+        <v>8.262330610793967</v>
       </c>
       <c r="N4" t="n">
-        <v>106.5146217427493</v>
+        <v>106.713050493393</v>
       </c>
       <c r="O4" t="n">
-        <v>10.32059212171226</v>
+        <v>10.33020089317691</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5144821669983</v>
+        <v>368.4310761133654</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25877,28 +25951,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4783250464284309</v>
+        <v>-0.4731796271768104</v>
       </c>
       <c r="J5" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K5" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09706226342279678</v>
+        <v>0.09563721457178986</v>
       </c>
       <c r="M5" t="n">
-        <v>8.675873993712356</v>
+        <v>8.675178502683302</v>
       </c>
       <c r="N5" t="n">
-        <v>118.3522572267435</v>
+        <v>118.2049576617152</v>
       </c>
       <c r="O5" t="n">
-        <v>10.87898236172591</v>
+        <v>10.87221033928774</v>
       </c>
       <c r="P5" t="n">
-        <v>362.9131750707314</v>
+        <v>362.8603030579272</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25955,28 +26029,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3798048046986688</v>
+        <v>-0.3767789394589316</v>
       </c>
       <c r="J6" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K6" t="n">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06590234123425343</v>
+        <v>0.06531405141655444</v>
       </c>
       <c r="M6" t="n">
-        <v>8.276142998897209</v>
+        <v>8.265871832025599</v>
       </c>
       <c r="N6" t="n">
-        <v>113.6934015409076</v>
+        <v>113.4227521658922</v>
       </c>
       <c r="O6" t="n">
-        <v>10.66271079702097</v>
+        <v>10.6500118387677</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5481023661721</v>
+        <v>357.5170103514709</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26014,7 +26088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G660"/>
+  <dimension ref="A1:G662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50437,6 +50511,80 @@
         </is>
       </c>
     </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-40.92666545156764,176.18652563931937</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-40.9270597951881,176.18579464059985</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-40.92735620043722,176.18496782168626</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-40.92769929403049,176.18418668553915</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-40.92804404727823,176.18340717600387</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-40.92665005658621,176.18651057676664</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-40.92704685756611,176.1857819824081</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-40.92734940634338,176.18496117439238</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-40.927688090949566,176.18417572460268</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-40.92803544616226,176.18339876085258</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G662"/>
+  <dimension ref="A1:G667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18310,6 +18310,141 @@
         <v>351.78</v>
       </c>
       <c r="G662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="C663" t="n">
+        <v>375.25</v>
+      </c>
+      <c r="D663" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="E663" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="F663" t="n">
+        <v>351.09</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:23+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>374.03</v>
+      </c>
+      <c r="C664" t="n">
+        <v>374.76</v>
+      </c>
+      <c r="D664" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="E664" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="F664" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>371.66</v>
+      </c>
+      <c r="C665" t="n">
+        <v>371.62</v>
+      </c>
+      <c r="D665" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="E665" t="n">
+        <v>354.05</v>
+      </c>
+      <c r="F665" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="C666" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="D666" t="n">
+        <v>359.6</v>
+      </c>
+      <c r="E666" t="n">
+        <v>353.64</v>
+      </c>
+      <c r="F666" t="n">
+        <v>347.32</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="C667" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="D667" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="E667" t="n">
+        <v>351.76</v>
+      </c>
+      <c r="F667" t="n">
+        <v>346.37</v>
+      </c>
+      <c r="G667" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18326,7 +18461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B722"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25549,6 +25684,56 @@
       </c>
       <c r="B722" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -25717,28 +25902,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5787609949274131</v>
+        <v>-0.5562830741438108</v>
       </c>
       <c r="J2" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="K2" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1446272573712166</v>
+        <v>0.135377054430044</v>
       </c>
       <c r="M2" t="n">
-        <v>8.392670436141518</v>
+        <v>8.436860966513505</v>
       </c>
       <c r="N2" t="n">
-        <v>110.6041997142895</v>
+        <v>111.4368126706148</v>
       </c>
       <c r="O2" t="n">
-        <v>10.51685312792232</v>
+        <v>10.55636361019337</v>
       </c>
       <c r="P2" t="n">
-        <v>372.1688840371821</v>
+        <v>371.9373699674398</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25795,28 +25980,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5586881912676819</v>
+        <v>-0.5370649508085115</v>
       </c>
       <c r="J3" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="K3" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1375112113987949</v>
+        <v>0.12875842005578</v>
       </c>
       <c r="M3" t="n">
-        <v>8.551741006181931</v>
+        <v>8.594339193481511</v>
       </c>
       <c r="N3" t="n">
-        <v>109.300509579896</v>
+        <v>110.0453941683185</v>
       </c>
       <c r="O3" t="n">
-        <v>10.45468840185569</v>
+        <v>10.49025234054541</v>
       </c>
       <c r="P3" t="n">
-        <v>372.3928389424274</v>
+        <v>372.1701448996583</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25873,28 +26058,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6027692558256675</v>
+        <v>-0.5894328008333164</v>
       </c>
       <c r="J4" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="K4" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1597253242980291</v>
+        <v>0.1553346461450092</v>
       </c>
       <c r="M4" t="n">
-        <v>8.262330610793967</v>
+        <v>8.267788895802324</v>
       </c>
       <c r="N4" t="n">
-        <v>106.713050493393</v>
+        <v>106.5222280259324</v>
       </c>
       <c r="O4" t="n">
-        <v>10.33020089317691</v>
+        <v>10.32096061546271</v>
       </c>
       <c r="P4" t="n">
-        <v>368.4310761133654</v>
+        <v>368.2937373854359</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25951,28 +26136,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4731796271768104</v>
+        <v>-0.4667553213559615</v>
       </c>
       <c r="J5" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="K5" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09563721457178986</v>
+        <v>0.09466600149892423</v>
       </c>
       <c r="M5" t="n">
-        <v>8.675178502683302</v>
+        <v>8.641776355505366</v>
       </c>
       <c r="N5" t="n">
-        <v>118.2049576617152</v>
+        <v>117.4758633782493</v>
       </c>
       <c r="O5" t="n">
-        <v>10.87221033928774</v>
+        <v>10.83862829781745</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8603030579272</v>
+        <v>362.7941634758806</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26029,28 +26214,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3767789394589316</v>
+        <v>-0.3747770168487923</v>
       </c>
       <c r="J6" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="K6" t="n">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06531405141655444</v>
+        <v>0.06570687284545085</v>
       </c>
       <c r="M6" t="n">
-        <v>8.265871832025599</v>
+        <v>8.217483369476316</v>
       </c>
       <c r="N6" t="n">
-        <v>113.4227521658922</v>
+        <v>112.6091159498258</v>
       </c>
       <c r="O6" t="n">
-        <v>10.6500118387677</v>
+        <v>10.61174424634451</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5170103514709</v>
+        <v>357.496430268346</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26088,7 +26273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G662"/>
+  <dimension ref="A1:G667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50585,6 +50770,191 @@
         </is>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-40.92663184280246,176.18649275629096</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-40.92703269122959,176.18576812204742</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-40.9273422508611,176.18495417352054</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-40.92767855026034,176.18416639013068</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-40.92803045896024,176.18339388148013</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:23+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-40.92663307151019,176.18649395846558</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-40.92702914964516,176.18576465695818</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-40.92733899836898,176.18495099130658</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-40.92768028493117,176.18416808730723</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-40.928027423271935,176.18339091142772</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-40.92661594187754,176.1864771987409</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-40.92700645459104,176.1857424521096</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-40.92731984480232,176.18493225160853</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-40.92766105899451,176.18414927693917</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-40.92801289533384,176.18337669760925</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-40.926611388430416,176.18647274362573</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-40.926995757557464,176.18573198613538</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-40.92731037643409,176.18492298783733</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-40.92765809559795,176.18414637759773</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-40.92800321004068,176.1833672217338</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-40.92658739248355,176.186449265886</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-40.926976604082455,176.1857132463928</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-40.92729924567952,176.18491209760592</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-40.927644507339444,176.1841330830598</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-40.92799634360093,176.1833605037641</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G667"/>
+  <dimension ref="A1:G673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18445,6 +18445,168 @@
         <v>346.37</v>
       </c>
       <c r="G667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>364.47</v>
+      </c>
+      <c r="C668" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="D668" t="n">
+        <v>356.73</v>
+      </c>
+      <c r="E668" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="F668" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="C669" t="n">
+        <v>365.17</v>
+      </c>
+      <c r="D669" t="n">
+        <v>356.84</v>
+      </c>
+      <c r="E669" t="n">
+        <v>350.72</v>
+      </c>
+      <c r="F669" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="C670" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="D670" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="E670" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="F670" t="n">
+        <v>345.28</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="C671" t="n">
+        <v>359.84</v>
+      </c>
+      <c r="D671" t="n">
+        <v>354.53</v>
+      </c>
+      <c r="E671" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="F671" t="n">
+        <v>344.32</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="C672" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="D672" t="n">
+        <v>354.88</v>
+      </c>
+      <c r="E672" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="F672" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="C673" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="D673" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="E673" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="F673" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="G673" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18461,7 +18623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25734,6 +25896,66 @@
       </c>
       <c r="B727" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -25902,28 +26124,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5562830741438108</v>
+        <v>-0.5503532408505772</v>
       </c>
       <c r="J2" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K2" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.135377054430044</v>
+        <v>0.135097726701215</v>
       </c>
       <c r="M2" t="n">
-        <v>8.436860966513505</v>
+        <v>8.389634520002456</v>
       </c>
       <c r="N2" t="n">
-        <v>111.4368126706148</v>
+        <v>110.6096125864946</v>
       </c>
       <c r="O2" t="n">
-        <v>10.55636361019337</v>
+        <v>10.51711046754262</v>
       </c>
       <c r="P2" t="n">
-        <v>371.9373699674398</v>
+        <v>371.8760412463831</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25980,28 +26202,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5370649508085115</v>
+        <v>-0.5295099032498248</v>
       </c>
       <c r="J3" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K3" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12875842005578</v>
+        <v>0.1276770917685386</v>
       </c>
       <c r="M3" t="n">
-        <v>8.594339193481511</v>
+        <v>8.555743004110823</v>
       </c>
       <c r="N3" t="n">
-        <v>110.0453941683185</v>
+        <v>109.2705898000009</v>
       </c>
       <c r="O3" t="n">
-        <v>10.49025234054541</v>
+        <v>10.45325737748769</v>
       </c>
       <c r="P3" t="n">
-        <v>372.1701448996583</v>
+        <v>372.0919858945878</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26058,28 +26280,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5894328008333164</v>
+        <v>-0.5843597724116307</v>
       </c>
       <c r="J4" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K4" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1553346461450092</v>
+        <v>0.1556592205918664</v>
       </c>
       <c r="M4" t="n">
-        <v>8.267788895802324</v>
+        <v>8.219512039891393</v>
       </c>
       <c r="N4" t="n">
-        <v>106.5222280259324</v>
+        <v>105.6560458583634</v>
       </c>
       <c r="O4" t="n">
-        <v>10.32096061546271</v>
+        <v>10.27891267879845</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2937373854359</v>
+        <v>368.2412503425361</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26136,28 +26358,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4667553213559615</v>
+        <v>-0.4684956442233616</v>
       </c>
       <c r="J5" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K5" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09466600149892423</v>
+        <v>0.09707921946869758</v>
       </c>
       <c r="M5" t="n">
-        <v>8.641776355505366</v>
+        <v>8.574992220633018</v>
       </c>
       <c r="N5" t="n">
-        <v>117.4758633782493</v>
+        <v>116.4461956878023</v>
       </c>
       <c r="O5" t="n">
-        <v>10.83862829781745</v>
+        <v>10.79102384798599</v>
       </c>
       <c r="P5" t="n">
-        <v>362.7941634758806</v>
+        <v>362.8121980832891</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26214,28 +26436,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3747770168487923</v>
+        <v>-0.3792553692816781</v>
       </c>
       <c r="J6" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="K6" t="n">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06570687284545085</v>
+        <v>0.06844572401726734</v>
       </c>
       <c r="M6" t="n">
-        <v>8.217483369476316</v>
+        <v>8.166175644951085</v>
       </c>
       <c r="N6" t="n">
-        <v>112.6091159498258</v>
+        <v>111.6647595640332</v>
       </c>
       <c r="O6" t="n">
-        <v>10.61174424634451</v>
+        <v>10.56715475253548</v>
       </c>
       <c r="P6" t="n">
-        <v>357.496430268346</v>
+        <v>357.5428006313479</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26273,7 +26495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G667"/>
+  <dimension ref="A1:G673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50955,6 +51177,228 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-40.926563974746976,176.18642635389165</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-40.926961064468074,176.18569804245877</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-40.927289632754174,176.18490269240908</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-40.92763547259212,176.18412424360946</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-40.927990850448815,176.18335512938933</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:54:16+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-40.926560722283156,176.18642317167152</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-40.92695983575428,176.18569684028756</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-40.92729042780819,176.1849034702824</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-40.92763699042973,176.18412572863693</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-40.92799439208641,176.18335859444664</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-40.926533040198045,176.18639608745517</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-40.926938369399195,176.18567583765653</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-40.92728500698527,176.18489816660102</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-40.927628823017606,176.18411773777552</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-40.927988465264264,176.18335279577954</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-40.92651692242712,176.18638031780452</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-40.92692131195568,176.18565914870706</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-40.927273731672706,176.18488713494665</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-40.92762072788283,176.18410981763174</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-40.92798152654524,176.18334600709744</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-40.926516561042064,176.186379964225</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-40.926922034728776,176.18565985586577</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-40.927276261390375,176.184889609997</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-40.92762636556605,176.18411533344596</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-40.92798564640972,176.18335003787726</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-40.926516561042064,176.186379964225</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-40.926922034728776,176.18565985586577</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-40.927264913799206,176.18487850762986</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-40.9276137169174,176.18410295822304</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-40.92797610567067,176.18334070344054</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0327/nzd0327.xlsx
+++ b/data/nzd0327/nzd0327.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G673"/>
+  <dimension ref="A1:G674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18595,7 +18595,7 @@
         <v>357.91</v>
       </c>
       <c r="C673" t="n">
-        <v>359.94</v>
+        <v>357.53</v>
       </c>
       <c r="D673" t="n">
         <v>353.31</v>
@@ -18607,6 +18607,33 @@
         <v>343.57</v>
       </c>
       <c r="G673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="C674" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="D674" t="n">
+        <v>352.46</v>
+      </c>
+      <c r="E674" t="n">
+        <v>346.31</v>
+      </c>
+      <c r="F674" t="n">
+        <v>343.16</v>
+      </c>
+      <c r="G674" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18623,7 +18650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B733"/>
+  <dimension ref="A1:B734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25956,6 +25983,16 @@
       </c>
       <c r="B733" t="n">
         <v>-0.52</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -26124,28 +26161,28 @@
         <v>0.0208</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5503532408505772</v>
+        <v>-0.5502290532821869</v>
       </c>
       <c r="J2" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K2" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L2" t="n">
-        <v>0.135097726701215</v>
+        <v>0.135442286899207</v>
       </c>
       <c r="M2" t="n">
-        <v>8.389634520002456</v>
+        <v>8.377753061659932</v>
       </c>
       <c r="N2" t="n">
-        <v>110.6096125864946</v>
+        <v>110.4455183680643</v>
       </c>
       <c r="O2" t="n">
-        <v>10.51711046754262</v>
+        <v>10.50930627434867</v>
       </c>
       <c r="P2" t="n">
-        <v>371.8760412463831</v>
+        <v>371.8747513495812</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26202,28 +26239,28 @@
         <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5295099032498248</v>
+        <v>-0.5304754930121346</v>
       </c>
       <c r="J3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1276770917685386</v>
+        <v>0.1284685586251628</v>
       </c>
       <c r="M3" t="n">
-        <v>8.555743004110823</v>
+        <v>8.541759148069536</v>
       </c>
       <c r="N3" t="n">
-        <v>109.2705898000009</v>
+        <v>109.1033806175013</v>
       </c>
       <c r="O3" t="n">
-        <v>10.45325737748769</v>
+        <v>10.44525636916113</v>
       </c>
       <c r="P3" t="n">
-        <v>372.0919858945878</v>
+        <v>372.102001413426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26280,28 +26317,28 @@
         <v>0.0307</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5843597724116307</v>
+        <v>-0.584394293775122</v>
       </c>
       <c r="J4" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K4" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1556592205918664</v>
+        <v>0.1561220598229978</v>
       </c>
       <c r="M4" t="n">
-        <v>8.219512039891393</v>
+        <v>8.207470493642269</v>
       </c>
       <c r="N4" t="n">
-        <v>105.6560458583634</v>
+        <v>105.4990732211016</v>
       </c>
       <c r="O4" t="n">
-        <v>10.27891267879845</v>
+        <v>10.2712741770971</v>
       </c>
       <c r="P4" t="n">
-        <v>368.2412503425361</v>
+        <v>368.2416089049666</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26358,28 +26395,28 @@
         <v>0.0274</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4684956442233616</v>
+        <v>-0.4696664782689379</v>
       </c>
       <c r="J5" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K5" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09707921946869758</v>
+        <v>0.0977997975892313</v>
       </c>
       <c r="M5" t="n">
-        <v>8.574992220633018</v>
+        <v>8.56806902612675</v>
       </c>
       <c r="N5" t="n">
-        <v>116.4461956878023</v>
+        <v>116.2961780092127</v>
       </c>
       <c r="O5" t="n">
-        <v>10.79102384798599</v>
+        <v>10.78407056770367</v>
       </c>
       <c r="P5" t="n">
-        <v>362.8121980832891</v>
+        <v>362.8243591643903</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26436,28 +26473,28 @@
         <v>0.0304</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3792553692816781</v>
+        <v>-0.3805070740289442</v>
       </c>
       <c r="J6" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K6" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06844572401726734</v>
+        <v>0.06907024186796118</v>
       </c>
       <c r="M6" t="n">
-        <v>8.166175644951085</v>
+        <v>8.160157279654779</v>
       </c>
       <c r="N6" t="n">
-        <v>111.6647595640332</v>
+        <v>111.5251346658497</v>
       </c>
       <c r="O6" t="n">
-        <v>10.56715475253548</v>
+        <v>10.5605461348289</v>
       </c>
       <c r="P6" t="n">
-        <v>357.5428006313479</v>
+        <v>357.5558016907241</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26495,7 +26532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G673"/>
+  <dimension ref="A1:G674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51375,7 +51412,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>-40.926922034728776,176.18565985586577</t>
+          <t>-40.92690461589598,176.18564281334545</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -51394,6 +51431,43 @@
         </is>
       </c>
       <c r="G673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-40.92651388679284,176.18637734773665</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-40.92690114658452,176.18563941898566</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-40.927258770198385,176.18487249679575</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-40.92760511583543,176.18409454307417</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-40.92797314225913,176.1833378041085</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
